--- a/sample/demo.xlsx
+++ b/sample/demo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>1. md2xls Feature Demo</t>
   </si>
@@ -40,10 +40,40 @@
     <t>be disabled via the heading_number: false config option or the --no-heading-number CLI flag.</t>
   </si>
   <si>
-    <t>1.1.2. Second H3 Under This Section</t>
-  </si>
-  <si>
-    <t>This is the second H3 under the same H2, so it should be numbered 1.2.2. in the output.</t>
+    <t>1.1.1.1. H4 Item Heading</t>
+  </si>
+  <si>
+    <t>This is an H4 heading. It should be numbered 1.2.1.1. in the output with 14pt bold font.</t>
+  </si>
+  <si>
+    <t>H5 SubItem Heading</t>
+  </si>
+  <si>
+    <t>This is an H5 heading. It should be numbered 1.2.1.1.1. with 12pt bold font.</t>
+  </si>
+  <si>
+    <t>H6 Detail Heading</t>
+  </si>
+  <si>
+    <t>This is an H6 heading. It should be numbered 1.2.1.1.1.1. with 11pt bold italic font.</t>
+  </si>
+  <si>
+    <t>1.1.1.2. Second H4</t>
+  </si>
+  <si>
+    <t>This verifies that the H4 counter increments correctly: 1.2.1.2..</t>
+  </si>
+  <si>
+    <t>1.1.2. Heading Counter Reset</t>
+  </si>
+  <si>
+    <t>After this H3, the H4/H5/H6 counters should reset. The next H4 should be 1.2.2.1..</t>
+  </si>
+  <si>
+    <t>1.1.2.1. Reset Verified</t>
+  </si>
+  <si>
+    <t>This H4 should be 1.2.2.1., not 1.2.2.3..</t>
   </si>
   <si>
     <t>1.2. Tables</t>
@@ -67,13 +97,13 @@
     <t>Supported</t>
   </si>
   <si>
-    <t>H1, H2, H3 with auto-numbering</t>
+    <t>H1-H6 with auto-numbering</t>
   </si>
   <si>
     <t>Tables</t>
   </si>
   <si>
-    <t>Header + data rows + borders</t>
+    <t>Header + data rows + alignment</t>
   </si>
   <si>
     <t>Code blocks</t>
@@ -97,37 +127,115 @@
     <t>Lists</t>
   </si>
   <si>
-    <t>Ordered, unordered, nested</t>
-  </si>
-  <si>
-    <t>Links</t>
-  </si>
-  <si>
-    <t>Excel hyperlinks</t>
-  </si>
-  <si>
-    <t>1.2.2. Wide Column Table</t>
+    <t>Ordered, unordered, task lists</t>
+  </si>
+  <si>
+    <t>Rich Text</t>
+  </si>
+  <si>
+    <t>Bold/italic in Excel cells</t>
+  </si>
+  <si>
+    <t>1.2.2. Table with Column Alignment</t>
+  </si>
+  <si>
+    <t>Left Aligned</t>
+  </si>
+  <si>
+    <t>Center Aligned</t>
+  </si>
+  <si>
+    <t>Right Aligned</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>$1.20</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>$0.50</t>
+  </si>
+  <si>
+    <t>Cherry</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>$3.00</t>
+  </si>
+  <si>
+    <t>1.2.3. Mixed Alignment Table</t>
   </si>
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Charlie</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>C+</t>
+  </si>
+  <si>
+    <t>1.2.4. Wide Column Table</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>This is a very long description that exceeds eighty bytes in length, so the column should be automatically merged across two Excel columns for readability</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Short</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>Another lengthy cell content designed to test the automatic column merging behavior when data exceeds the eighty byte threshold in md2xls</t>
@@ -243,6 +351,69 @@
     <t xml:space="preserve">    2. Nested ordered 2</t>
   </si>
   <si>
+    <t>1.6.4. Task Lists</t>
+  </si>
+  <si>
+    <t>☐ Design the new feature</t>
+  </si>
+  <si>
+    <t>☐ Write unit tests</t>
+  </si>
+  <si>
+    <t>☑ Set up the project structure</t>
+  </si>
+  <si>
+    <t>☑ Implement the parser</t>
+  </si>
+  <si>
+    <t>☐ Write documentation</t>
+  </si>
+  <si>
+    <t>1.6.5. Nested Task Lists</t>
+  </si>
+  <si>
+    <t>☐ Release v2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ☑ Implement H4-H6 headings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ☑ Add task list support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ☑ Add table alignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ☑ Add rich text formatting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ☐ Final QA testing</t>
+  </si>
+  <si>
+    <t>☑ Release v1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ☑ Core Markdown parsing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ☑ Excel rendering</t>
+  </si>
+  <si>
+    <t>1.6.6. Mixed Task and Regular Lists</t>
+  </si>
+  <si>
+    <t>☑ Completed task</t>
+  </si>
+  <si>
+    <t>☐ Pending task</t>
+  </si>
+  <si>
+    <t>• Regular bullet item (not a task)</t>
+  </si>
+  <si>
+    <t>☑ Another completed task</t>
+  </si>
+  <si>
     <t>1.7. Links &amp; Hyperlinks</t>
   </si>
   <si>
@@ -255,16 +426,209 @@
     <t>This line has multiple links inside it.</t>
   </si>
   <si>
-    <t>1.8. Inline Formatting</t>
-  </si>
-  <si>
-    <t>This text has bold words, italic words, and inline code mixed together.</t>
-  </si>
-  <si>
-    <t>Here is a link to example within a sentence.</t>
-  </si>
-  <si>
-    <t>All inline formatting markers are stripped in the Excel output, leaving clean readable text.</t>
+    <t>1.8. Inline Formatting (Rich Text)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve">This text has </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t>bold words</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve"> rendered in Excel with actual bold formatting.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve">This text has </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <i val="1"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t>italic words</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve"> rendered in Excel with actual italic formatting.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve">This text has </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <b val="1"/>
+        <i val="1"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t>bold and italic</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve"> rendered together in a single cell.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t>Bold</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve"> at the start, </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <i val="1"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t>italic</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve"> in the middle, and </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t>bold again</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve"> at the end.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve">Here is a mix of </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <b val="1"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t>bold</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <i val="1"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t>italic</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="游ゴシック Regular"/>
+        <family val="2"/>
+        <color/>
+        <sz val="11"/>
+      </rPr>
+      <t>, and inline code in one line.</t>
+    </r>
+  </si>
+  <si>
+    <t>Plain text without any formatting markers stays as-is.</t>
   </si>
   <si>
     <t>1.9. HTML Entities</t>
@@ -354,6 +718,24 @@
     <t>This should be numbered 2.1.1. in the output.</t>
   </si>
   <si>
+    <t>2.1.1.1. Deep Nesting Under Second H1</t>
+  </si>
+  <si>
+    <t>This should be 2.1.1.1. — verifying counters reset properly across H1 boundaries.</t>
+  </si>
+  <si>
+    <t>Even Deeper</t>
+  </si>
+  <si>
+    <t>Numbered 2.1.1.1.1..</t>
+  </si>
+  <si>
+    <t>Maximum Depth</t>
+  </si>
+  <si>
+    <t>Numbered 2.1.1.1.1.1..</t>
+  </si>
+  <si>
     <t>2.1.2. Another Subsection</t>
   </si>
   <si>
@@ -366,10 +748,10 @@
     <t>This demo file covers all md2xls features:</t>
   </si>
   <si>
-    <t>1. Headings (H1-H3) with auto-numbering</t>
-  </si>
-  <si>
-    <t>2. Tables with auto-sizing columns</t>
+    <t>1. Headings (H1-H6) with auto-numbering</t>
+  </si>
+  <si>
+    <t>2. Tables with column alignment (left, center, right)</t>
   </si>
   <si>
     <t>3. Fenced code blocks with language tags</t>
@@ -384,26 +766,29 @@
     <t>6. Lists (ordered, unordered, nested)</t>
   </si>
   <si>
-    <t>7. Links rendered as Excel hyperlinks</t>
-  </si>
-  <si>
-    <t>8. Inline formatting (bold, italic, code, links)</t>
-  </si>
-  <si>
-    <t>9. HTML entity decoding</t>
-  </si>
-  <si>
-    <t>10. Horizontal rules</t>
-  </si>
-  <si>
-    <t>11. Word-boundary-aware text wrapping</t>
+    <t>7. Task lists with checkboxes</t>
+  </si>
+  <si>
+    <t>8. Links rendered as Excel hyperlinks</t>
+  </si>
+  <si>
+    <t>9. Inline rich text formatting (bold, italic in Excel cells)</t>
+  </si>
+  <si>
+    <t>10. HTML entity decoding</t>
+  </si>
+  <si>
+    <t>11. Horizontal rules</t>
+  </si>
+  <si>
+    <t>12. Word-boundary-aware text wrapping</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -436,6 +821,28 @@
       <b val="1"/>
       <color/>
       <sz val="16"/>
+    </font>
+    <font>
+      <name val="游ゴシック Regular"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="游ゴシック Regular"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="游ゴシック Regular"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -527,7 +934,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment vertical="center"/>
@@ -541,22 +948,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="false">
@@ -902,7 +1327,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -922,16 +1347,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
@@ -939,7 +1357,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -949,143 +1367,79 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="5" t="s">
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="5" t="s">
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="s">
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="6" t="s">
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="s">
-        <v>30</v>
+      <c r="A30" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="5"/>
-    </row>
-    <row r="33" ht="105" customHeight="true">
-      <c r="A33" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="7"/>
-    </row>
-    <row r="34" ht="105" customHeight="true">
-      <c r="A34" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="7"/>
-    </row>
-    <row r="35" ht="105" customHeight="true">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="7"/>
+      <c r="A32" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
@@ -1094,7 +1448,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1111,7 +1465,7 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
@@ -1121,201 +1475,220 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="s">
+      <c r="B52" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="s">
-        <v>1</v>
+      <c r="C52" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
+      <c r="A53" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
+      <c r="A54" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
+      <c r="A55" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
+      <c r="A56" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
+      <c r="A57" s="4" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
+      <c r="A58" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
+      <c r="A59" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
+      <c r="A60" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="s">
-        <v>1</v>
+      <c r="A61" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="s">
-        <v>44</v>
+      <c r="A62" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="63">
@@ -1324,63 +1697,50 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
+      <c r="A64" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
+      <c r="A65" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
+      <c r="A66" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>71</v>
+      </c>
       <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
+    </row>
+    <row r="67" ht="105" customHeight="true">
+      <c r="A67" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" s="9"/>
+    </row>
+    <row r="68" ht="105" customHeight="true">
+      <c r="A68" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="9"/>
+    </row>
+    <row r="69" ht="105" customHeight="true">
+      <c r="A69" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" s="9"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
@@ -1388,140 +1748,133 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
+      <c r="A71" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
     </row>
     <row r="72">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
+      <c r="A72" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
+      <c r="A73" s="4" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
+      <c r="A74" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="9"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
+      <c r="A75" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A76" s="14"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A77" s="14"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A78" s="14"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14"/>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
+      <c r="A79" s="14"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
     </row>
     <row r="80">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
+      <c r="A80" s="14"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="14"/>
     </row>
     <row r="81">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
+      <c r="A81" s="14"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A82" s="14"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
+      <c r="A83" s="14"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14"/>
     </row>
     <row r="84">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
+      <c r="A84" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="9"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
+      <c r="A85" s="4" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
@@ -1529,93 +1882,160 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
+      <c r="A87" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A88" s="14"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A89" s="14"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A90" s="14"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="14"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A92" s="14"/>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="14"/>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A93" s="14"/>
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="14"/>
+      <c r="B94" s="14"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="14"/>
+      <c r="H94" s="14"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="s">
-        <v>1</v>
+      <c r="A96" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
+      <c r="A97" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A98" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B98" s="14"/>
+      <c r="C98" s="14"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="14"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
+      <c r="H98" s="14"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A99" s="14"/>
+      <c r="B99" s="14"/>
+      <c r="C99" s="14"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
+      <c r="H99" s="14"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A100" s="14"/>
+      <c r="B100" s="14"/>
+      <c r="C100" s="14"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
+      <c r="H100" s="14"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="A101" s="14"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="14"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>57</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="A103" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
@@ -1623,29 +2043,56 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="A105" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B105" s="15"/>
+      <c r="C105" s="15"/>
+      <c r="D105" s="15"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="15"/>
+      <c r="G105" s="15"/>
+      <c r="H105" s="15"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A106" s="15"/>
+      <c r="B106" s="15"/>
+      <c r="C106" s="15"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="15"/>
+      <c r="G106" s="15"/>
+      <c r="H106" s="15"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="A107" s="15"/>
+      <c r="B107" s="15"/>
+      <c r="C107" s="15"/>
+      <c r="D107" s="15"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="15"/>
+      <c r="G107" s="15"/>
+      <c r="H107" s="15"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="A108" s="15"/>
+      <c r="B108" s="15"/>
+      <c r="C108" s="15"/>
+      <c r="D108" s="15"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="15"/>
+      <c r="G108" s="15"/>
+      <c r="H108" s="15"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="s">
-        <v>62</v>
-      </c>
+      <c r="A109" s="15"/>
+      <c r="B109" s="15"/>
+      <c r="C109" s="15"/>
+      <c r="D109" s="15"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="15"/>
+      <c r="G109" s="15"/>
+      <c r="H109" s="15"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
@@ -1653,8 +2100,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="s">
-        <v>63</v>
+      <c r="A111" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="112">
@@ -1663,246 +2110,251 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="A113" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B113" s="15"/>
+      <c r="C113" s="15"/>
+      <c r="D113" s="15"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="15"/>
+      <c r="G113" s="15"/>
+      <c r="H113" s="15"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="A114" s="15"/>
+      <c r="B114" s="15"/>
+      <c r="C114" s="15"/>
+      <c r="D114" s="15"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="15"/>
+      <c r="G114" s="15"/>
+      <c r="H114" s="15"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="A115" s="15"/>
+      <c r="B115" s="15"/>
+      <c r="C115" s="15"/>
+      <c r="D115" s="15"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="15"/>
+      <c r="G115" s="15"/>
+      <c r="H115" s="15"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="s">
-        <v>68</v>
-      </c>
+      <c r="A117" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B117" s="15"/>
+      <c r="C117" s="15"/>
+      <c r="D117" s="15"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="15"/>
+      <c r="G117" s="15"/>
+      <c r="H117" s="15"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="A118" s="15"/>
+      <c r="B118" s="15"/>
+      <c r="C118" s="15"/>
+      <c r="D118" s="15"/>
+      <c r="E118" s="15"/>
+      <c r="F118" s="15"/>
+      <c r="G118" s="15"/>
+      <c r="H118" s="15"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="A119" s="15"/>
+      <c r="B119" s="15"/>
+      <c r="C119" s="15"/>
+      <c r="D119" s="15"/>
+      <c r="E119" s="15"/>
+      <c r="F119" s="15"/>
+      <c r="G119" s="15"/>
+      <c r="H119" s="15"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A121" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
-      <c r="G122" s="3"/>
-      <c r="H122" s="3"/>
+      <c r="A122" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="s">
-        <v>1</v>
+      <c r="A123" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="s">
+      <c r="A124" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="s">
-        <v>74</v>
+      <c r="A126" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="s">
-        <v>1</v>
+      <c r="A127" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="s">
+      <c r="A128" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B130" s="3"/>
-      <c r="C130" s="3"/>
-      <c r="D130" s="3"/>
-      <c r="E130" s="3"/>
-      <c r="F130" s="3"/>
-      <c r="G130" s="3"/>
-      <c r="H130" s="3"/>
+      <c r="A130" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A131" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="s">
-        <v>1</v>
+      <c r="A133" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="10" t="s">
-        <v>78</v>
+      <c r="A134" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>1</v>
+        <v>94</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B138" s="3"/>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3"/>
-      <c r="E138" s="3"/>
-      <c r="F138" s="3"/>
-      <c r="G138" s="3"/>
-      <c r="H138" s="3"/>
+      <c r="A138" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="s">
-        <v>1</v>
+      <c r="A139" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>1</v>
+        <v>96</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="s">
-        <v>1</v>
+      <c r="A145" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-      <c r="F148" s="3"/>
-      <c r="G148" s="3"/>
-      <c r="H148" s="3"/>
+      <c r="A148" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>1</v>
+        <v>102</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" ht="8" customHeight="true">
-      <c r="A152" s="11"/>
-      <c r="B152" s="11"/>
-      <c r="C152" s="11"/>
-      <c r="D152" s="11"/>
-      <c r="E152" s="11"/>
-      <c r="F152" s="11"/>
-      <c r="G152" s="11"/>
-      <c r="H152" s="11"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>1</v>
+        <v>106</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
     </row>
     <row r="155">
@@ -1910,15 +2362,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" ht="8" customHeight="true">
-      <c r="A156" s="11"/>
-      <c r="B156" s="11"/>
-      <c r="C156" s="11"/>
-      <c r="D156" s="11"/>
-      <c r="E156" s="11"/>
-      <c r="F156" s="11"/>
-      <c r="G156" s="11"/>
-      <c r="H156" s="11"/>
+    <row r="156">
+      <c r="A156" s="4" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
@@ -1927,32 +2374,27 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" ht="8" customHeight="true">
-      <c r="A160" s="11"/>
-      <c r="B160" s="11"/>
-      <c r="C160" s="11"/>
-      <c r="D160" s="11"/>
-      <c r="E160" s="11"/>
-      <c r="F160" s="11"/>
-      <c r="G160" s="11"/>
-      <c r="H160" s="11"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
     </row>
     <row r="163">
@@ -1961,16 +2403,9 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B164" s="3"/>
-      <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
-      <c r="E164" s="3"/>
-      <c r="F164" s="3"/>
-      <c r="G164" s="3"/>
-      <c r="H164" s="3"/>
+      <c r="A164" s="4" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
@@ -1978,48 +2413,48 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="4" t="s">
-        <v>91</v>
+      <c r="A166" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="s">
-        <v>95</v>
+      <c r="A172" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>1</v>
+        <v>122</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
     </row>
     <row r="175">
@@ -2029,7 +2464,7 @@
     </row>
     <row r="176">
       <c r="A176" s="4" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
     </row>
     <row r="177">
@@ -2039,30 +2474,23 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>1</v>
+        <v>127</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B181" s="3"/>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3"/>
-      <c r="E181" s="3"/>
-      <c r="F181" s="3"/>
-      <c r="G181" s="3"/>
-      <c r="H181" s="3"/>
+      <c r="A181" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
@@ -2070,9 +2498,16 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="4" t="s">
-        <v>101</v>
-      </c>
+      <c r="A183" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
@@ -2080,8 +2515,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="s">
-        <v>102</v>
+      <c r="A185" s="16" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="186">
@@ -2090,8 +2525,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="4" t="s">
-        <v>103</v>
+      <c r="A187" s="16" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="188">
@@ -2100,8 +2535,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="s">
-        <v>104</v>
+      <c r="A189" s="16" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="190">
@@ -2110,9 +2545,16 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="s">
-        <v>105</v>
-      </c>
+      <c r="A191" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="3"/>
+      <c r="F191" s="3"/>
+      <c r="G191" s="3"/>
+      <c r="H191" s="3"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
@@ -2120,16 +2562,9 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B193" s="3"/>
-      <c r="C193" s="3"/>
-      <c r="D193" s="3"/>
-      <c r="E193" s="3"/>
-      <c r="F193" s="3"/>
-      <c r="G193" s="3"/>
-      <c r="H193" s="3"/>
+      <c r="A193" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
@@ -2137,8 +2572,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="4" t="s">
-        <v>107</v>
+      <c r="A195" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="196">
@@ -2148,7 +2583,7 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
     </row>
     <row r="198">
@@ -2157,8 +2592,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="4" t="s">
-        <v>109</v>
+      <c r="A199" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="200">
@@ -2168,7 +2603,7 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
     </row>
     <row r="202">
@@ -2177,16 +2612,9 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B203" s="3"/>
-      <c r="C203" s="3"/>
-      <c r="D203" s="3"/>
-      <c r="E203" s="3"/>
-      <c r="F203" s="3"/>
-      <c r="G203" s="3"/>
-      <c r="H203" s="3"/>
+      <c r="A203" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
@@ -2194,9 +2622,16 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="A205" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="3"/>
+      <c r="F205" s="3"/>
+      <c r="G205" s="3"/>
+      <c r="H205" s="3"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
@@ -2205,57 +2640,64 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>114</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>118</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>120</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="s">
-        <v>121</v>
-      </c>
+      <c r="A215" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B215" s="3"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
+      <c r="E215" s="3"/>
+      <c r="F215" s="3"/>
+      <c r="G215" s="3"/>
+      <c r="H215" s="3"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
-        <v>122</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
     </row>
     <row r="218">
@@ -2263,24 +2705,466 @@
         <v>1</v>
       </c>
     </row>
+    <row r="219" ht="8" customHeight="true">
+      <c r="A219" s="17"/>
+      <c r="B219" s="17"/>
+      <c r="C219" s="17"/>
+      <c r="D219" s="17"/>
+      <c r="E219" s="17"/>
+      <c r="F219" s="17"/>
+      <c r="G219" s="17"/>
+      <c r="H219" s="17"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" ht="8" customHeight="true">
+      <c r="A223" s="17"/>
+      <c r="B223" s="17"/>
+      <c r="C223" s="17"/>
+      <c r="D223" s="17"/>
+      <c r="E223" s="17"/>
+      <c r="F223" s="17"/>
+      <c r="G223" s="17"/>
+      <c r="H223" s="17"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" ht="8" customHeight="true">
+      <c r="A227" s="17"/>
+      <c r="B227" s="17"/>
+      <c r="C227" s="17"/>
+      <c r="D227" s="17"/>
+      <c r="E227" s="17"/>
+      <c r="F227" s="17"/>
+      <c r="G227" s="17"/>
+      <c r="H227" s="17"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B231" s="3"/>
+      <c r="C231" s="3"/>
+      <c r="D231" s="3"/>
+      <c r="E231" s="3"/>
+      <c r="F231" s="3"/>
+      <c r="G231" s="3"/>
+      <c r="H231" s="3"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B248" s="3"/>
+      <c r="C248" s="3"/>
+      <c r="D248" s="3"/>
+      <c r="E248" s="3"/>
+      <c r="F248" s="3"/>
+      <c r="G248" s="3"/>
+      <c r="H248" s="3"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B260" s="3"/>
+      <c r="C260" s="3"/>
+      <c r="D260" s="3"/>
+      <c r="E260" s="3"/>
+      <c r="F260" s="3"/>
+      <c r="G260" s="3"/>
+      <c r="H260" s="3"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B282" s="3"/>
+      <c r="C282" s="3"/>
+      <c r="D282" s="3"/>
+      <c r="E282" s="3"/>
+      <c r="F282" s="3"/>
+      <c r="G282" s="3"/>
+      <c r="H282" s="3"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A41:H49"/>
-    <mergeCell ref="A53:H60"/>
-    <mergeCell ref="A64:H67"/>
-    <mergeCell ref="A71:H75"/>
-    <mergeCell ref="A79:H81"/>
-    <mergeCell ref="A83:H85"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="A75:H83"/>
+    <mergeCell ref="A87:H94"/>
+    <mergeCell ref="A98:H101"/>
+    <mergeCell ref="A105:H109"/>
+    <mergeCell ref="A113:H115"/>
+    <mergeCell ref="A117:H119"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A124" r:id="rId1"/>
-    <hyperlink ref="A126" r:id="rId2"/>
-    <hyperlink ref="A128" r:id="rId3"/>
-    <hyperlink ref="A134" r:id="rId4"/>
+    <hyperlink ref="A185" r:id="rId1"/>
+    <hyperlink ref="A187" r:id="rId2"/>
+    <hyperlink ref="A189" r:id="rId3"/>
   </hyperlinks>
 </worksheet>
 </file>